--- a/artfynd/A 63138-2025 artfynd.xlsx
+++ b/artfynd/A 63138-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134167458</v>
+        <v>134167250</v>
       </c>
       <c r="B2" t="n">
         <v>57162</v>
@@ -718,14 +718,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Marielund, Ramnäs, Marielund, Ramnäs, Vstm</t>
+          <t>Marielund, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563722</v>
+        <v>563710</v>
       </c>
       <c r="R2" t="n">
-        <v>6629444</v>
+        <v>6629445</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,7 +798,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134167250</v>
+        <v>134167458</v>
       </c>
       <c r="B3" t="n">
         <v>57162</v>
@@ -841,14 +841,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Marielund, Ramnäs, Vstm</t>
+          <t>Marielund, Ramnäs, Marielund, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563710</v>
+        <v>563722</v>
       </c>
       <c r="R3" t="n">
-        <v>6629445</v>
+        <v>6629444</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,6 +918,123 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>89962833</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hopmilsvad, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>563712</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6629359</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-01-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-01-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kärrkant mot hygge</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63138-2025 artfynd.xlsx
+++ b/artfynd/A 63138-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134167250</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Skogsprojektet</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134167458</t>
         </is>
       </c>
     </row>
@@ -1035,8 +1050,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89962833</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>